--- a/e2e/expectedData/sub_Master_Prorate.xlsx
+++ b/e2e/expectedData/sub_Master_Prorate.xlsx
@@ -83,10 +83,10 @@
     <t>14-Jan-26</t>
   </si>
   <si>
-    <t>$ 175.48</t>
-  </si>
-  <si>
-    <t>$ -175.48</t>
+    <t>$ 216.77</t>
+  </si>
+  <si>
+    <t>$ -216.77</t>
   </si>
   <si>
     <t>15-Jan-26</t>
@@ -95,16 +95,16 @@
     <t>31-Jan-26</t>
   </si>
   <si>
-    <t>$ 466.13</t>
-  </si>
-  <si>
-    <t>$ 641.61</t>
+    <t>$ 575.81</t>
+  </si>
+  <si>
+    <t>$ 792.58</t>
   </si>
   <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>DILI, 26 AGUSTUS 2026</t>
+    <t>DILI, 09 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>

--- a/e2e/expectedData/sub_Master_Prorate.xlsx
+++ b/e2e/expectedData/sub_Master_Prorate.xlsx
@@ -104,7 +104,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>DILI, 09 SEPTEMBER 2026</t>
+    <t>DILI, 10 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
